--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED12.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED12.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>157W</t>
+          <t>162W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0128</t>
+          <t>SIM_XA_FIXED-2-0160</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>122W</t>
+          <t>28W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0季</t>
+          <t>2季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,14 +1748,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0021</t>
+          <t>SIM_XA_FIXED-3-0084</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99W</t>
+          <t>140W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>第4年</t>
+          <t>第3年</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>5季</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>3季</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G53"/>
+  <dimension ref="B2:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2189,14 +2189,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auction_Win</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2215,23 +2215,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E17" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>第2年2季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2241,14 +2241,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E18" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-ba6f2ff6bb", "line_id": "L-a12c8bc8f4", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2267,23 +2267,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-48</v>
+        <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>380</v>
+        <v>418</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2293,14 +2293,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E20" t="n">
-        <v>348</v>
+        <v>404</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-6b9631fc81", "line_id": "L-a12c8bc8f4", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2319,14 +2319,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E21" t="n">
-        <v>334</v>
+        <v>389</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-a12c8bc8f4"}</t>
         </is>
       </c>
     </row>
@@ -2345,14 +2345,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>319</v>
+        <v>389</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-a12c8bc8f4"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a12c8bc8f4", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>319</v>
+        <v>389</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a12c8bc8f4", "asset_type": "factory"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a12c8bc8f4", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>319</v>
+        <v>389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a12c8bc8f4", "asset_type": "production_line"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-2-0160", "receivable_term_quarters": 2, "revenue_wan": 28.0}</t>
         </is>
       </c>
     </row>
@@ -2423,14 +2423,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-12</v>
       </c>
       <c r="E25" t="n">
-        <v>307</v>
+        <v>377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2449,14 +2449,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E26" t="n">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-08334aba79", "line_id": "L-a12c8bc8f4", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2475,23 +2475,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>122</v>
+        <v>-12</v>
       </c>
       <c r="E27" t="n">
-        <v>415</v>
+        <v>357</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0128", "receivable_term_quarters": 0, "revenue_wan": 122.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2501,23 +2501,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-48</v>
+        <v>-14</v>
       </c>
       <c r="E28" t="n">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2527,14 +2527,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E29" t="n">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-712fd3717f", "line_id": "L-a12c8bc8f4", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2553,14 +2553,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-14</v>
+        <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-71eb0ceeb4"}</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
         <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2605,14 +2605,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-14</v>
+        <v>-36</v>
       </c>
       <c r="E32" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -2631,14 +2631,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-15</v>
+        <v>-24</v>
       </c>
       <c r="E33" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-a12c8bc8f4"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-de46c8417d", "line_id": "L-a12c8bc8f4", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E34" t="n">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a12c8bc8f4", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2683,14 +2683,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E35" t="n">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a12c8bc8f4", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-a12c8bc8f4"}</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2709,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a12c8bc8f4", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2735,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a12c8bc8f4", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2761,23 +2761,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E38" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2794,11 +2794,11 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2820,16 +2820,16 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-4-0021", "receivable_term_quarters": 4, "revenue_wan": 99.0}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0084", "receivable_term_quarters": 3, "revenue_wan": 140.0}</t>
         </is>
       </c>
     </row>
@@ -2846,11 +2846,11 @@
         <v>-48</v>
       </c>
       <c r="E41" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2872,16 +2872,16 @@
         <v>-32</v>
       </c>
       <c r="E42" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-840ae1c85f", "line_id": "L-a12c8bc8f4", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-7a16d4cd0a", "line_id": "L-a12c8bc8f4", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2898,11 +2898,11 @@
         <v>-14</v>
       </c>
       <c r="E43" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2917,23 +2917,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E44" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-a12c8bc8f4"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2943,14 +2943,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a12c8bc8f4", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2969,14 +2969,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E46" t="n">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a12c8bc8f4", "asset_type": "production_line"}</t>
+          <t>receivable_collected | {"receivable_id": "AR-a0f9fe5b24"}</t>
         </is>
       </c>
     </row>
@@ -2995,23 +2995,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E47" t="n">
-        <v>101</v>
+        <v>231</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-a12c8bc8f4"}</t>
         </is>
       </c>
     </row>
@@ -3021,23 +3021,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>87</v>
+        <v>231</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a12c8bc8f4", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3047,23 +3047,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>73</v>
+        <v>231</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a12c8bc8f4", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -3073,23 +3073,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>99</v>
+        <v>-12</v>
       </c>
       <c r="E50" t="n">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-1911a9989f"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -3099,23 +3099,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E51" t="n">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-a12c8bc8f4"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3125,23 +3125,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E52" t="n">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a12c8bc8f4", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3151,21 +3151,99 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E53" t="n">
+        <v>177</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>第5年3季</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Pay_Maintenance</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E54" t="n">
+        <v>162</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>maintenance_expense | {"line_id": "L-a12c8bc8f4"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>157</v>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>162</v>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>第5年4季</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a12c8bc8f4", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>162</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a12c8bc8f4", "asset_type": "production_line"}</t>
         </is>
@@ -3281,7 +3359,7 @@
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3506,7 +3584,7 @@
         <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -3562,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3587,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
         <v>80</v>
@@ -3612,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3643,7 +3721,7 @@
         <v>83</v>
       </c>
       <c r="H19" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3662,13 +3740,13 @@
         <v>-83</v>
       </c>
       <c r="F20" t="n">
-        <v>-41</v>
+        <v>-75</v>
       </c>
       <c r="G20" t="n">
-        <v>-64</v>
+        <v>-23</v>
       </c>
       <c r="H20" t="n">
-        <v>-57</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="21">
@@ -3712,13 +3790,13 @@
         <v>-98.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-56.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-79.2</v>
+        <v>-38.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-72.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="23">
@@ -3759,16 +3837,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-108.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-56.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-79.2</v>
+        <v>-38.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-72.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="25">
@@ -3809,16 +3887,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-108.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-56.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-79.2</v>
+        <v>-38.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-72.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="28">
@@ -3908,16 +3986,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>319</v>
+        <v>389</v>
       </c>
       <c r="F30" t="n">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="G30" t="n">
-        <v>115</v>
+        <v>231</v>
       </c>
       <c r="H30" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31">
@@ -3939,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3958,13 +4036,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G32" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3983,13 +4061,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" t="n">
         <v>80</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>80</v>
@@ -4033,16 +4111,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F35" t="n">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="G35" t="n">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="H35" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36">
@@ -4158,16 +4236,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>480.6</v>
+        <v>490.6</v>
       </c>
       <c r="F40" t="n">
-        <v>424.4</v>
+        <v>400.4</v>
       </c>
       <c r="G40" t="n">
-        <v>345.2</v>
+        <v>362.2</v>
       </c>
       <c r="H40" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41">
@@ -4336,13 +4414,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-194.4</v>
+        <v>-184.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-250.6</v>
+        <v>-274.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-329.8</v>
+        <v>-312.8</v>
       </c>
     </row>
     <row r="48">
@@ -4358,16 +4436,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-108.2</v>
+        <v>-98.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-56.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-79.2</v>
+        <v>-38.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-72.2</v>
+        <v>-84.2</v>
       </c>
     </row>
     <row r="49">
@@ -4383,16 +4461,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>480.6</v>
+        <v>490.6</v>
       </c>
       <c r="F49" t="n">
-        <v>424.4</v>
+        <v>400.4</v>
       </c>
       <c r="G49" t="n">
-        <v>345.2</v>
+        <v>362.2</v>
       </c>
       <c r="H49" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50">
@@ -4408,16 +4486,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>480.6</v>
+        <v>490.6</v>
       </c>
       <c r="F50" t="n">
-        <v>424.4</v>
+        <v>400.4</v>
       </c>
       <c r="G50" t="n">
-        <v>345.2</v>
+        <v>362.2</v>
       </c>
       <c r="H50" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -4488,7 +4566,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4637,7 +4715,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4786,7 +4864,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4935,7 +5013,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5084,7 +5162,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
